--- a/Documents/devfiles/excel/CandidateResponse.xlsx
+++ b/Documents/devfiles/excel/CandidateResponse.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitLab\joboffer\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitLab\joboffer\Documents\devfiles\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06A6D0AA-BA98-44F3-A763-08643446B591}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E803FD74-7397-4D03-A0CB-7FA2069B28C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Responses" sheetId="1" r:id="rId1"/>
@@ -1047,7 +1047,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3517,7 +3517,7 @@
       </c>
     </row>
     <row r="9" spans="2:3">
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
@@ -3612,7 +3612,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="21" spans="2:3" ht="29">
+    <row r="21" spans="2:3">
       <c r="B21" s="5" t="s">
         <v>19</v>
       </c>
@@ -3652,7 +3652,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="26" spans="2:3" ht="29">
+    <row r="26" spans="2:3">
       <c r="B26" s="5" t="s">
         <v>224</v>
       </c>
@@ -3660,7 +3660,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="27" spans="2:3" ht="29">
+    <row r="27" spans="2:3" ht="25">
       <c r="B27" s="5" t="s">
         <v>25</v>
       </c>
@@ -3668,7 +3668,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="28" spans="2:3" ht="29">
+    <row r="28" spans="2:3">
       <c r="B28" s="5" t="s">
         <v>26</v>
       </c>
@@ -3676,7 +3676,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="29" spans="2:3" ht="29">
+    <row r="29" spans="2:3">
       <c r="B29" s="5" t="s">
         <v>27</v>
       </c>
@@ -3684,7 +3684,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="30" spans="2:3" ht="29">
+    <row r="30" spans="2:3">
       <c r="B30" s="5" t="s">
         <v>28</v>
       </c>
